--- a/04_DESIGN_TABLES/DesignTable_5404_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5404_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ26"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,17 +2221,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5404-16-06</t>
+          <t>5404-16-04</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1.96</v>
       </c>
       <c r="C15" t="n">
-        <v>0.79674</v>
+        <v>0.79386</v>
       </c>
       <c r="D15" t="n">
-        <v>1.38</v>
+        <v>1.375</v>
       </c>
       <c r="E15" t="n">
         <v>0.6415999999999999</v>
@@ -2261,55 +2261,55 @@
         <v>0.57203</v>
       </c>
       <c r="N15" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="P15" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="R15" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="T15" t="n">
         <v>0.05556</v>
       </c>
       <c r="U15" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="V15" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="W15" t="n">
         <v>1.96</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="Y15" t="n">
         <v>1.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.41</v>
+        <v>0.281</v>
       </c>
       <c r="AA15" t="n">
         <v>0.79</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>5404-16-06</t>
+          <t>5404-16-04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 3/8-18 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2334,23 +2334,28 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>NPTF ends: Brennan nipple STEPs (measured; family validated) + ASME B1.20.3; L/hex/bores: Air-Way (single source) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-16-04 column 'L LGTH' = 1.960 (catalog_verified.json); OMi Items row 1283: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-16-04 column 'C HEX' = 1.375 (catalog_verified.json); OMi Items row 1283: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-16-04 column 'A1 DRILL' = 0.938 (catalog_verified.json); OMi Items row 1283: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-16-04 column 'A2 DRILL' = 0.281 (catalog_verified.json); OMi Items row 1283: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[16] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[4] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] thread text; equals the 2026-10-02 proposal | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5404-16-06</t>
+          <t>5404-16-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5404-16-08</t>
+          <t>5404-16-06</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="C16" t="n">
         <v>0.79674</v>
@@ -2386,34 +2391,34 @@
         <v>0.57203</v>
       </c>
       <c r="N16" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="P16" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="R16" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="T16" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="U16" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="V16" t="n">
-        <v>0.35064</v>
+        <v>0.28378</v>
       </c>
       <c r="W16" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
         <v>0.9399999999999999</v>
@@ -2422,19 +2427,19 @@
         <v>1.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>5404-16-08</t>
+          <t>5404-16-06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 1/2-14 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2449,7 +2454,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2464,14 +2469,14 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5404-16-08</t>
+          <t>5404-16-06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5404-16-12</t>
+          <t>5404-16-08</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2511,31 +2516,31 @@
         <v>0.57203</v>
       </c>
       <c r="N17" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="P17" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="T17" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="V17" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="W17" t="n">
         <v>2.15</v>
@@ -2547,19 +2552,19 @@
         <v>1.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="AA17" t="n">
         <v>0.98</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>5404-16-12</t>
+          <t>5404-16-08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 3/4-14 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2574,7 +2579,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2589,18 +2594,18 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5404-16-12</t>
+          <t>5404-16-08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5404-16-16</t>
+          <t>5404-16-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="C18" t="n">
         <v>0.79674</v>
@@ -2636,34 +2641,34 @@
         <v>0.57203</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="P18" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="T18" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="V18" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="W18" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="X18" t="n">
         <v>0.9399999999999999</v>
@@ -2672,19 +2677,19 @@
         <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.17</v>
+        <v>0.98</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>5404-16-16</t>
+          <t>5404-16-12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 1-11 1/2 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2699,7 +2704,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2714,51 +2719,51 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5404-16-16</t>
+          <t>5404-16-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5404-20-16</t>
+          <t>5404-16-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="C19" t="n">
-        <v>1.01036</v>
+        <v>0.79674</v>
       </c>
       <c r="D19" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="E19" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="G19" t="n">
         <v>1.7899</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="K19" t="n">
         <v>0.08696</v>
       </c>
       <c r="L19" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="N19" t="n">
         <v>0.6415999999999999</v>
@@ -2788,28 +2793,28 @@
         <v>0.57203</v>
       </c>
       <c r="W19" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z19" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>5404-20-16</t>
+          <t>5404-16-16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1 1/4-11 1/2 NPTF x 1-11 1/2 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1-11 1/2 NPTF x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -2819,7 +2824,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2839,18 +2844,18 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>5404-20-16</t>
+          <t>5404-16-16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5404-20-20</t>
+          <t>5404-20-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="C20" t="n">
         <v>1.01036</v>
@@ -2886,34 +2891,34 @@
         <v>0.74378</v>
       </c>
       <c r="N20" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="P20" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2632</v>
+        <v>0.2043</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6267</v>
+        <v>1.02482</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="V20" t="n">
-        <v>0.74378</v>
+        <v>0.45527</v>
       </c>
       <c r="W20" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="X20" t="n">
         <v>1.25</v>
@@ -2922,19 +2927,19 @@
         <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.25</v>
+        <v>0.719</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>5404-20-20</t>
+          <t>5404-20-12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1 1/4-11 1/2 NPTF x 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -2949,7 +2954,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2959,56 +2964,61 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>NPTF ends: Brennan nipple STEPs (measured; family validated) + ASME B1.20.3; L/hex/bores: Air-Way (single source) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-20-12 column 'L LGTH' = 2.260 (catalog_verified.json); OMi Items row 1288: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-20-12 column 'C HEX' = 1.750 (catalog_verified.json); OMi Items row 1288: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-20-12 column 'A1 DRILL' = 1.250 (catalog_verified.json); OMi Items row 1288: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-20-12 column 'A2 DRILL' = 0.719 (catalog_verified.json); OMi Items row 1288: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[20] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[12] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12] thread text; equals the 2026-10-02 proposal | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>5404-20-20</t>
+          <t>5404-20-12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5404-24-16</t>
+          <t>5404-20-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1547</v>
+        <v>1.01036</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E21" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="G21" t="n">
         <v>1.7899</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2765</v>
+        <v>0.2632</v>
       </c>
       <c r="I21" t="n">
-        <v>1.86566</v>
+        <v>1.6267</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="K21" t="n">
         <v>0.08696</v>
       </c>
       <c r="L21" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="M21" t="n">
-        <v>0.86326</v>
+        <v>0.74378</v>
       </c>
       <c r="N21" t="n">
         <v>0.6415999999999999</v>
@@ -3038,28 +3048,28 @@
         <v>0.57203</v>
       </c>
       <c r="W21" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="X21" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.305</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.245</v>
+        <v>1.21</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>5404-24-16</t>
+          <t>5404-20-16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1 1/2-11 1/2 NPTF x 1-11 1/2 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1 1/4-11 1/2 NPTF x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3069,7 +3079,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3089,51 +3099,51 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>5404-24-16</t>
+          <t>5404-20-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5404-24-20</t>
+          <t>5404-20-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1547</v>
+        <v>1.01036</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E22" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="G22" t="n">
         <v>1.7899</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2765</v>
+        <v>0.2632</v>
       </c>
       <c r="I22" t="n">
-        <v>1.86566</v>
+        <v>1.6267</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="K22" t="n">
         <v>0.08696</v>
       </c>
       <c r="L22" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="M22" t="n">
-        <v>0.86326</v>
+        <v>0.74378</v>
       </c>
       <c r="N22" t="n">
         <v>0.81335</v>
@@ -3163,28 +3173,28 @@
         <v>0.74378</v>
       </c>
       <c r="W22" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="X22" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.305</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
         <v>1.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>5404-24-20</t>
+          <t>5404-20-20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1 1/2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3194,7 +3204,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3214,18 +3224,18 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>5404-24-20</t>
+          <t>5404-20-20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5404-24-24</t>
+          <t>5404-24-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="C23" t="n">
         <v>1.1547</v>
@@ -3261,55 +3271,55 @@
         <v>0.86326</v>
       </c>
       <c r="N23" t="n">
-        <v>0.93283</v>
+        <v>0.51241</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7235</v>
+        <v>0.5457</v>
       </c>
       <c r="P23" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2765</v>
+        <v>0.2043</v>
       </c>
       <c r="R23" t="n">
-        <v>1.86566</v>
+        <v>1.02482</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7235</v>
+        <v>0.5457</v>
       </c>
       <c r="T23" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.93283</v>
+        <v>0.51241</v>
       </c>
       <c r="V23" t="n">
-        <v>0.86326</v>
+        <v>0.45527</v>
       </c>
       <c r="W23" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="X23" t="n">
         <v>1.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.305</v>
+        <v>1.315</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>0.719</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.305</v>
+        <v>1.065</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>5404-24-24</t>
+          <t>5404-24-12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1 1/2-11 1/2 NPTF x 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3324,7 +3334,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -3334,107 +3344,112 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>NPTF ends: Brennan nipple STEPs (measured; family validated) + ASME B1.20.3; L/hex/bores: Air-Way (single source) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-24-12 column 'L LGTH' = 2.380 (catalog_verified.json); OMi Items row 1291: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-24-12 column 'C HEX' = 2.000 (catalog_verified.json); OMi Items row 1291: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-24-12 column 'A1 DRILL' = 1.500 (catalog_verified.json); OMi Items row 1291: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-24-12 column 'A2 DRILL' = 0.719 (catalog_verified.json); OMi Items row 1291: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[24] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[12] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12] thread text; equals the 2026-10-02 proposal | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>5404-24-24</t>
+          <t>5404-24-12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5404-32-20</t>
+          <t>5404-24-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="C24" t="n">
-        <v>1.44338</v>
+        <v>1.1547</v>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="G24" t="n">
         <v>1.7899</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2735</v>
+        <v>0.2765</v>
       </c>
       <c r="I24" t="n">
-        <v>2.33859</v>
+        <v>1.86566</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="K24" t="n">
         <v>0.08696</v>
       </c>
       <c r="L24" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09973</v>
+        <v>0.86326</v>
       </c>
       <c r="N24" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="P24" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="T24" t="n">
         <v>0.08696</v>
       </c>
       <c r="U24" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="W24" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="X24" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>1.305</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.35</v>
+        <v>1.245</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>5404-32-20</t>
+          <t>5404-24-16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1 1/2-11 1/2 NPTF x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3444,127 +3459,122 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>CONFLICT-BORES</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>NPTF ends: Brennan nipple STEPs + ASME B1.20.3; L=2.76 &amp; hex=2.50 VERIFIED (Brennan drawing 2026-09-06) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>RESOLVED: page A/D columns confirmed swapped (Brennan title+drawing: end 1 = 2-11-1/2). Threads/bores reordered to PN order. OPEN CONFLICT: bores - AW 1.78/1.13 vs Brennan drawing O1.938/O1.250; no third source yet (J514 140137C row would settle it) - AW retained, do not machine bores without tiebreak</t>
+          <t>NPTF ends: Brennan nipple STEPs (measured; family validated) + ASME B1.20.3; L/hex/bores: Air-Way (single source) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>5404-32-20</t>
+          <t>5404-24-16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5404-32-24</t>
+          <t>5404-24-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="C25" t="n">
-        <v>1.44338</v>
+        <v>1.1547</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="G25" t="n">
         <v>1.7899</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2735</v>
+        <v>0.2765</v>
       </c>
       <c r="I25" t="n">
-        <v>2.33859</v>
+        <v>1.86566</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="K25" t="n">
         <v>0.08696</v>
       </c>
       <c r="L25" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09973</v>
+        <v>0.86326</v>
       </c>
       <c r="N25" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="P25" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2765</v>
+        <v>0.2632</v>
       </c>
       <c r="R25" t="n">
-        <v>1.86566</v>
+        <v>1.6267</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="T25" t="n">
         <v>0.08696</v>
       </c>
       <c r="U25" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="V25" t="n">
-        <v>0.86326</v>
+        <v>0.74378</v>
       </c>
       <c r="W25" t="n">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="X25" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.41</v>
+        <v>1.305</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.38</v>
+        <v>1.275</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>5404-32-24</t>
+          <t>5404-24-20</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hexagon Pipe Nipple, 2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF</t>
+          <t>Hexagon Pipe Nipple, 1 1/2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -3574,12 +3584,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3594,132 +3604,902 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>5404-32-24</t>
+          <t>5404-24-20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5404-32-32</t>
+          <t>5404-24-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.82</v>
+        <v>2.61</v>
       </c>
       <c r="C26" t="n">
-        <v>1.44338</v>
+        <v>1.1547</v>
       </c>
       <c r="D26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="G26" t="n">
         <v>1.7899</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2735</v>
+        <v>0.2765</v>
       </c>
       <c r="I26" t="n">
-        <v>2.33859</v>
+        <v>1.86566</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="K26" t="n">
         <v>0.08696</v>
       </c>
       <c r="L26" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09973</v>
+        <v>0.86326</v>
       </c>
       <c r="N26" t="n">
-        <v>1.16929</v>
+        <v>0.93283</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="P26" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2735</v>
+        <v>0.2765</v>
       </c>
       <c r="R26" t="n">
-        <v>2.33859</v>
+        <v>1.86566</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7565</v>
+        <v>0.7235</v>
       </c>
       <c r="T26" t="n">
         <v>0.08696</v>
       </c>
       <c r="U26" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>5404-24-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Nipple, 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>NPTF ends: Brennan nipple STEPs (measured; family validated) + ASME B1.20.3; L/hex/bores: Air-Way (single source) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>5404-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5404-32-12</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E27" t="n">
         <v>1.16929</v>
       </c>
-      <c r="V26" t="n">
+      <c r="F27" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M27" t="n">
         <v>1.09973</v>
       </c>
-      <c r="W26" t="n">
+      <c r="N27" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>5404-32-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Nipple, 2-11 1/2 NPTF x 3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-12 column 'L LGTH' = 2.540 (catalog_verified.json); OMi Items row 1295: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-12 column 'C HEX' = 2.500 (catalog_verified.json); OMi Items row 1295: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-12 column 'A1 DRILL' = 1.938 (catalog_verified.json); OMi Items row 1295: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-12 column 'A2 DRILL' = 0.719 (catalog_verified.json); OMi Items row 1295: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[32] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[12] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12] thread text; equals the 2026-10-02 proposal | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>5404-32-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5404-32-16</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.57203</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>5404-32-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Nipple, 2-11 1/2 NPTF x 1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-16 column 'L LGTH' = 2.630 (catalog_verified.json); OMi Items row 1296: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-16 column 'C HEX' = 2.500 (catalog_verified.json); OMi Items row 1296: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-16 column 'A1 DRILL' = 1.938 (catalog_verified.json); OMi Items row 1296: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-16 column 'A2 DRILL' = 0.938 (catalog_verified.json); OMi Items row 1296: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[32] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[16] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16] thread text; equals the 2026-10-02 proposal | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>5404-32-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5404-32-20</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>5404-32-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Nipple, 2-11 1/2 NPTF x 1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>CONFLICT-BORES</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>NPTF ends: Brennan nipple STEPs + ASME B1.20.3; L=2.76 &amp; hex=2.50 VERIFIED (Brennan drawing 2026-09-06) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>RESOLVED: page A/D columns confirmed swapped (Brennan title+drawing: end 1 = 2-11-1/2). Threads/bores reordered to PN order. OPEN CONFLICT: bores - AW 1.78/1.13 vs Brennan drawing O1.938/O1.250; no third source yet (J514 140137C row would settle it) - AW retained, do not machine bores without tiebreak</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>5404-32-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5404-32-24</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>5404-32-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Nipple, 2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>NPTF ends: Brennan nipple STEPs (measured; family validated) + ASME B1.20.3; L/hex/bores: Air-Way (single source) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>5404-32-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5404-32-32</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>2.82</v>
       </c>
-      <c r="X26" t="n">
+      <c r="C31" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.94</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y31" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z31" t="n">
         <v>1.94</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AA31" t="n">
         <v>1.41</v>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>5404-32-32</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>Hexagon Pipe Nipple, 2-11 1/2 NPTF x 2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>5404</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>NPTF ends: Brennan nipple STEPs (measured; family validated) + ASME B1.20.3; L/hex/bores: Air-Way (single source) | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400)</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>5404-32-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5404-40-40</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.73205</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.40977</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.1374</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.81954</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.1374</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.40977</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.30977</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.40977</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.1374</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.81954</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.1374</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.40977</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.30977</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>5404-40-40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hexagon Pipe Nipple, 2 1/2-8 NPTF x 2 1/2-8 NPTF</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>2 1/2-8 NPTF</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>2 1/2-8 NPTF</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: NPTF male ends per ASME B1.20.3 (tip = E0+0.8P, cone L2 at 1.7899 deg) + Brennan-measured end length (5404 table); bore step at the hex mid-plane (ASSUMPTION, as 2403/6400); -40 PIPE END (2-1/2-8 NPTF) IS BRENNAN-MEASURED, NOT ASME B1.20.1 (user 2026-10-02: Brennan-measured threads accepted for -40): male end - pitch dia at the tip E0 2.71954 = the Brennan blank cone 2.7769 (5404-40-40 / 5406-40-32 / 2501-40-40-FG STEPs) - 0.4589 P (the Brennan blank sits 0.4585-0.4595 P above ASME E0 at all 8 library sizes -04..-32, ASSUMED to hold at -40), crest E0 + 0.8P, taper 1.7899deg, thread length L2 1.1374 from D = E0 + 0.8P + (L2 - 2P)/16 with pipe OD D 2.875 (Brennan collar), end length 1.515 (measured on all four Brennan -40 male ends); female port - tap drill 2.729 and thread depth 1.0443 = the Brennan 5000-40-40 tapered port (no separate drill: the 2.729 bore runs through); 8 threads per inch = Brennan TFA catalog callout 2-1/2-8; single manufacturer, ASSUMED</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / bores from the Brennan TFA catalog p11 alone; the -40 NPTF ends are not in the end library</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>5404-40-40</t>
         </is>
       </c>
     </row>
